--- a/IONQ.xlsx
+++ b/IONQ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA1A146-E8B6-47D6-927A-EC78318E9D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C68CEA7-62C9-44AE-93B0-22E3F5F6C0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22150" windowHeight="20350" activeTab="1" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
+    <workbookView xWindow="6120" yWindow="4500" windowWidth="23600" windowHeight="13830" activeTab="1" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,11 @@
     Q424 guidance: 75-95m
 83m consensus
 Q225 guidance: 82-100m
-Q325 guidance: 106-110m</t>
+Q325 guidance: 106-110m
+8.7m from Vector
+21.5m from Capella
+18.8m from ID quantique
+48m from acquisitions</t>
       </text>
     </comment>
   </commentList>
@@ -928,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -975,6 +979,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -999,14 +1007,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>23141</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>52449</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>23141</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>52449</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>43542</xdr:rowOff>
     </xdr:to>
@@ -1023,7 +1031,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13729372" y="0"/>
+          <a:off x="14374141" y="0"/>
           <a:ext cx="0" cy="11996196"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1557,7 +1565,11 @@
     <text>Q424 guidance: 75-95m
 83m consensus
 Q225 guidance: 82-100m
-Q325 guidance: 106-110m</text>
+Q325 guidance: 106-110m
+8.7m from Vector
+21.5m from Capella
+18.8m from ID quantique
+48m from acquisitions</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1582,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>55</v>
+        <v>31.53</v>
       </c>
       <c r="N2" s="1"/>
       <c r="Q2" s="1"/>
@@ -1596,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="4">
-        <v>354.27959099999998</v>
+        <v>368.98291699999999</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1614,7 +1626,7 @@
       </c>
       <c r="J4" s="4">
         <f>+J2*J3</f>
-        <v>19485.377505</v>
+        <v>11634.031373010001</v>
       </c>
       <c r="N4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1628,11 +1640,11 @@
         <v>3</v>
       </c>
       <c r="J5" s="4">
-        <f>657+1000</f>
-        <v>1657</v>
+        <f>1030.865+1361.291+944.643</f>
+        <v>3336.799</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1646,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="13" x14ac:dyDescent="0.3">
@@ -1658,7 +1670,7 @@
       </c>
       <c r="J7" s="4">
         <f>+J4-J5+J6</f>
-        <v>17828.377505</v>
+        <v>8297.2323730099997</v>
       </c>
       <c r="N7" s="4"/>
       <c r="Q7" s="4"/>
@@ -3019,15 +3031,15 @@
       </c>
       <c r="R17" s="22">
         <f t="shared" si="9"/>
-        <v>64.252499999999998</v>
+        <v>99.142499999999984</v>
       </c>
       <c r="S17" s="22">
         <f>+SUM(T30:AB30)-S20</f>
-        <v>85.805999999999997</v>
+        <v>323.69600000000003</v>
       </c>
       <c r="T17" s="22">
         <f>+SUM(U30:AC30)-T20</f>
-        <v>32.916000000000004</v>
+        <v>270.80599999999998</v>
       </c>
       <c r="AF17" s="23"/>
       <c r="AH17" s="23"/>
@@ -3610,11 +3622,22 @@
         <v>39.866</v>
       </c>
       <c r="V30" s="13">
-        <v>27</v>
+        <v>61.89</v>
       </c>
       <c r="W30" s="13">
-        <f>+V30</f>
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="X30" s="13">
+        <f>+W30+5</f>
+        <v>55</v>
+      </c>
+      <c r="Y30" s="13">
+        <f>+X30+5</f>
+        <v>60</v>
+      </c>
+      <c r="Z30" s="13">
+        <f>+Y30+5</f>
+        <v>65</v>
       </c>
       <c r="AC30" s="13">
         <v>0.2</v>
@@ -3636,308 +3659,308 @@
         <v>43.073</v>
       </c>
       <c r="AI30" s="13">
-        <f>+AH30*1.9</f>
-        <v>81.838700000000003</v>
+        <f>SUM(S30:V30)</f>
+        <v>130.02249999999998</v>
       </c>
       <c r="AJ30" s="13">
         <f>+AI30*1.9</f>
-        <v>155.49352999999999</v>
+        <v>247.04274999999996</v>
       </c>
       <c r="AK30" s="13">
         <f>+AJ30*1.9</f>
-        <v>295.43770699999999</v>
+        <v>469.38122499999992</v>
       </c>
       <c r="AL30" s="13">
         <f>+AK30*1.9</f>
-        <v>561.3316433</v>
+        <v>891.82432749999975</v>
       </c>
       <c r="AM30" s="13">
         <f>+AL30*1.9</f>
-        <v>1066.53012227</v>
+        <v>1694.4662222499994</v>
       </c>
       <c r="AN30" s="13">
         <f>+AM30*1.1</f>
-        <v>1173.1831344970001</v>
+        <v>1863.9128444749995</v>
       </c>
       <c r="AO30" s="13">
         <f t="shared" ref="AO30:AS30" si="12">+AN30*1.1</f>
-        <v>1290.5014479467002</v>
+        <v>2050.3041289224998</v>
       </c>
       <c r="AP30" s="13">
         <f t="shared" si="12"/>
-        <v>1419.5515927413703</v>
+        <v>2255.3345418147501</v>
       </c>
       <c r="AQ30" s="13">
         <f t="shared" si="12"/>
-        <v>1561.5067520155076</v>
+        <v>2480.8679959962251</v>
       </c>
       <c r="AR30" s="13">
         <f t="shared" si="12"/>
-        <v>1717.6574272170585</v>
+        <v>2728.9547955958478</v>
       </c>
       <c r="AS30" s="13">
         <f t="shared" si="12"/>
-        <v>1889.4231699387644</v>
+        <v>3001.8502751554329</v>
       </c>
       <c r="AT30" s="13">
         <f>+AS30*1.1</f>
-        <v>2078.365486932641</v>
+        <v>3302.0353026709763</v>
       </c>
       <c r="AU30" s="13">
         <f t="shared" ref="AU30:DF30" si="13">+AT30*1.1</f>
-        <v>2286.2020356259054</v>
+        <v>3632.2388329380742</v>
       </c>
       <c r="AV30" s="13">
         <f t="shared" si="13"/>
-        <v>2514.822239188496</v>
+        <v>3995.462716231882</v>
       </c>
       <c r="AW30" s="13">
         <f t="shared" si="13"/>
-        <v>2766.3044631073458</v>
+        <v>4395.0089878550707</v>
       </c>
       <c r="AX30" s="13">
         <f t="shared" si="13"/>
-        <v>3042.9349094180807</v>
+        <v>4834.5098866405779</v>
       </c>
       <c r="AY30" s="13">
         <f t="shared" si="13"/>
-        <v>3347.2284003598888</v>
+        <v>5317.9608753046359</v>
       </c>
       <c r="AZ30" s="13">
         <f t="shared" si="13"/>
-        <v>3681.9512403958779</v>
+        <v>5849.7569628351002</v>
       </c>
       <c r="BA30" s="13">
         <f t="shared" si="13"/>
-        <v>4050.1463644354662</v>
+        <v>6434.7326591186111</v>
       </c>
       <c r="BB30" s="13">
         <f t="shared" si="13"/>
-        <v>4455.161000879013</v>
+        <v>7078.2059250304728</v>
       </c>
       <c r="BC30" s="13">
         <f t="shared" si="13"/>
-        <v>4900.6771009669146</v>
+        <v>7786.0265175335207</v>
       </c>
       <c r="BD30" s="13">
         <f t="shared" si="13"/>
-        <v>5390.7448110636069</v>
+        <v>8564.6291692868726</v>
       </c>
       <c r="BE30" s="13">
         <f t="shared" si="13"/>
-        <v>5929.8192921699683</v>
+        <v>9421.0920862155599</v>
       </c>
       <c r="BF30" s="13">
         <f t="shared" si="13"/>
-        <v>6522.8012213869661</v>
+        <v>10363.201294837118</v>
       </c>
       <c r="BG30" s="13">
         <f t="shared" si="13"/>
-        <v>7175.0813435256632</v>
+        <v>11399.52142432083</v>
       </c>
       <c r="BH30" s="13">
         <f t="shared" si="13"/>
-        <v>7892.5894778782304</v>
+        <v>12539.473566752915</v>
       </c>
       <c r="BI30" s="13">
         <f t="shared" si="13"/>
-        <v>8681.848425666054</v>
+        <v>13793.420923428208</v>
       </c>
       <c r="BJ30" s="13">
         <f t="shared" si="13"/>
-        <v>9550.0332682326607</v>
+        <v>15172.76301577103</v>
       </c>
       <c r="BK30" s="13">
         <f t="shared" si="13"/>
-        <v>10505.036595055928</v>
+        <v>16690.039317348135</v>
       </c>
       <c r="BL30" s="13">
         <f t="shared" si="13"/>
-        <v>11555.540254561522</v>
+        <v>18359.043249082952</v>
       </c>
       <c r="BM30" s="13">
         <f t="shared" si="13"/>
-        <v>12711.094280017674</v>
+        <v>20194.947573991249</v>
       </c>
       <c r="BN30" s="13">
         <f t="shared" si="13"/>
-        <v>13982.203708019442</v>
+        <v>22214.442331390375</v>
       </c>
       <c r="BO30" s="13">
         <f t="shared" si="13"/>
-        <v>15380.424078821388</v>
+        <v>24435.886564529414</v>
       </c>
       <c r="BP30" s="13">
         <f t="shared" si="13"/>
-        <v>16918.466486703528</v>
+        <v>26879.475220982356</v>
       </c>
       <c r="BQ30" s="13">
         <f t="shared" si="13"/>
-        <v>18610.313135373883</v>
+        <v>29567.422743080595</v>
       </c>
       <c r="BR30" s="13">
         <f t="shared" si="13"/>
-        <v>20471.344448911274</v>
+        <v>32524.165017388656</v>
       </c>
       <c r="BS30" s="13">
         <f t="shared" si="13"/>
-        <v>22518.478893802403</v>
+        <v>35776.581519127525</v>
       </c>
       <c r="BT30" s="13">
         <f t="shared" si="13"/>
-        <v>24770.326783182645</v>
+        <v>39354.239671040283</v>
       </c>
       <c r="BU30" s="13">
         <f t="shared" si="13"/>
-        <v>27247.359461500913</v>
+        <v>43289.663638144317</v>
       </c>
       <c r="BV30" s="13">
         <f t="shared" si="13"/>
-        <v>29972.095407651006</v>
+        <v>47618.630001958751</v>
       </c>
       <c r="BW30" s="13">
         <f t="shared" si="13"/>
-        <v>32969.304948416109</v>
+        <v>52380.493002154632</v>
       </c>
       <c r="BX30" s="13">
         <f t="shared" si="13"/>
-        <v>36266.235443257727</v>
+        <v>57618.542302370101</v>
       </c>
       <c r="BY30" s="13">
         <f t="shared" si="13"/>
-        <v>39892.858987583502</v>
+        <v>63380.396532607119</v>
       </c>
       <c r="BZ30" s="13">
         <f t="shared" si="13"/>
-        <v>43882.144886341855</v>
+        <v>69718.436185867831</v>
       </c>
       <c r="CA30" s="13">
         <f t="shared" si="13"/>
-        <v>48270.359374976048</v>
+        <v>76690.279804454622</v>
       </c>
       <c r="CB30" s="13">
         <f t="shared" si="13"/>
-        <v>53097.395312473658</v>
+        <v>84359.307784900084</v>
       </c>
       <c r="CC30" s="13">
         <f t="shared" si="13"/>
-        <v>58407.134843721025</v>
+        <v>92795.238563390099</v>
       </c>
       <c r="CD30" s="13">
         <f t="shared" si="13"/>
-        <v>64247.848328093132</v>
+        <v>102074.76241972912</v>
       </c>
       <c r="CE30" s="13">
         <f t="shared" si="13"/>
-        <v>70672.633160902449</v>
+        <v>112282.23866170204</v>
       </c>
       <c r="CF30" s="13">
         <f t="shared" si="13"/>
-        <v>77739.896476992697</v>
+        <v>123510.46252787225</v>
       </c>
       <c r="CG30" s="13">
         <f t="shared" si="13"/>
-        <v>85513.88612469197</v>
+        <v>135861.5087806595</v>
       </c>
       <c r="CH30" s="13">
         <f t="shared" si="13"/>
-        <v>94065.274737161177</v>
+        <v>149447.65965872546</v>
       </c>
       <c r="CI30" s="13">
         <f t="shared" si="13"/>
-        <v>103471.8022108773</v>
+        <v>164392.42562459802</v>
       </c>
       <c r="CJ30" s="13">
         <f t="shared" si="13"/>
-        <v>113818.98243196504</v>
+        <v>180831.66818705783</v>
       </c>
       <c r="CK30" s="13">
         <f t="shared" si="13"/>
-        <v>125200.88067516155</v>
+        <v>198914.83500576363</v>
       </c>
       <c r="CL30" s="13">
         <f t="shared" si="13"/>
-        <v>137720.96874267771</v>
+        <v>218806.31850634</v>
       </c>
       <c r="CM30" s="13">
         <f t="shared" si="13"/>
-        <v>151493.0656169455</v>
+        <v>240686.95035697403</v>
       </c>
       <c r="CN30" s="13">
         <f t="shared" si="13"/>
-        <v>166642.37217864007</v>
+        <v>264755.64539267146</v>
       </c>
       <c r="CO30" s="13">
         <f t="shared" si="13"/>
-        <v>183306.60939650409</v>
+        <v>291231.20993193862</v>
       </c>
       <c r="CP30" s="13">
         <f t="shared" si="13"/>
-        <v>201637.27033615453</v>
+        <v>320354.3309251325</v>
       </c>
       <c r="CQ30" s="13">
         <f t="shared" si="13"/>
-        <v>221800.99736976999</v>
+        <v>352389.76401764579</v>
       </c>
       <c r="CR30" s="13">
         <f t="shared" si="13"/>
-        <v>243981.09710674701</v>
+        <v>387628.7404194104</v>
       </c>
       <c r="CS30" s="13">
         <f t="shared" si="13"/>
-        <v>268379.20681742171</v>
+        <v>426391.61446135148</v>
       </c>
       <c r="CT30" s="13">
         <f t="shared" si="13"/>
-        <v>295217.12749916391</v>
+        <v>469030.77590748668</v>
       </c>
       <c r="CU30" s="13">
         <f t="shared" si="13"/>
-        <v>324738.84024908033</v>
+        <v>515933.8534982354</v>
       </c>
       <c r="CV30" s="13">
         <f t="shared" si="13"/>
-        <v>357212.72427398839</v>
+        <v>567527.23884805897</v>
       </c>
       <c r="CW30" s="13">
         <f t="shared" si="13"/>
-        <v>392933.99670138728</v>
+        <v>624279.96273286489</v>
       </c>
       <c r="CX30" s="13">
         <f t="shared" si="13"/>
-        <v>432227.39637152606</v>
+        <v>686707.95900615142</v>
       </c>
       <c r="CY30" s="13">
         <f t="shared" si="13"/>
-        <v>475450.1360086787</v>
+        <v>755378.75490676658</v>
       </c>
       <c r="CZ30" s="13">
         <f t="shared" si="13"/>
-        <v>522995.14960954664</v>
+        <v>830916.63039744331</v>
       </c>
       <c r="DA30" s="13">
         <f t="shared" si="13"/>
-        <v>575294.66457050131</v>
+        <v>914008.29343718768</v>
       </c>
       <c r="DB30" s="13">
         <f t="shared" si="13"/>
-        <v>632824.13102755148</v>
+        <v>1005409.1227809065</v>
       </c>
       <c r="DC30" s="13">
         <f t="shared" si="13"/>
-        <v>696106.54413030669</v>
+        <v>1105950.0350589973</v>
       </c>
       <c r="DD30" s="13">
         <f t="shared" si="13"/>
-        <v>765717.19854333741</v>
+        <v>1216545.0385648971</v>
       </c>
       <c r="DE30" s="13">
         <f t="shared" si="13"/>
-        <v>842288.91839767119</v>
+        <v>1338199.542421387</v>
       </c>
       <c r="DF30" s="13">
         <f t="shared" si="13"/>
-        <v>926517.81023743842</v>
+        <v>1472019.4966635259</v>
       </c>
     </row>
     <row r="31" spans="2:110" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -3996,8 +4019,7 @@
         <v>21.253</v>
       </c>
       <c r="V31" s="10">
-        <f>+V30-V32</f>
-        <v>13.5</v>
+        <v>43.593000000000004</v>
       </c>
       <c r="AD31" s="10">
         <v>0.14299999999999999</v>
@@ -4017,47 +4039,47 @@
       </c>
       <c r="AI31" s="10">
         <f>+AI30-AI32</f>
-        <v>24.551610000000004</v>
+        <v>39.006749999999997</v>
       </c>
       <c r="AJ31" s="10">
         <f t="shared" ref="AJ31:AS31" si="14">+AJ30-AJ32</f>
-        <v>46.648059000000003</v>
+        <v>74.112824999999987</v>
       </c>
       <c r="AK31" s="10">
         <f t="shared" si="14"/>
-        <v>88.631312100000002</v>
+        <v>140.8143675</v>
       </c>
       <c r="AL31" s="10">
         <f t="shared" si="14"/>
-        <v>168.39949299</v>
+        <v>267.54729824999993</v>
       </c>
       <c r="AM31" s="10">
         <f t="shared" si="14"/>
-        <v>319.95903668100004</v>
+        <v>508.33986667499994</v>
       </c>
       <c r="AN31" s="10">
         <f t="shared" si="14"/>
-        <v>351.95494034910007</v>
+        <v>559.17385334250002</v>
       </c>
       <c r="AO31" s="10">
         <f t="shared" si="14"/>
-        <v>387.15043438401017</v>
+        <v>615.09123867674998</v>
       </c>
       <c r="AP31" s="10">
         <f t="shared" si="14"/>
-        <v>425.86547782241121</v>
+        <v>676.60036254442502</v>
       </c>
       <c r="AQ31" s="10">
         <f t="shared" si="14"/>
-        <v>468.45202560465236</v>
+        <v>744.26039879886753</v>
       </c>
       <c r="AR31" s="10">
         <f t="shared" si="14"/>
-        <v>515.29722816511753</v>
+        <v>818.68643867875448</v>
       </c>
       <c r="AS31" s="10">
         <f t="shared" si="14"/>
-        <v>566.82695098162935</v>
+        <v>900.55508254662982</v>
       </c>
     </row>
     <row r="32" spans="2:110" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4116,21 +4138,21 @@
         <f>+R30-R31</f>
         <v>6.6650000000000009</v>
       </c>
-      <c r="S32" s="11">
+      <c r="S32" s="24">
         <f>+S30-S31</f>
         <v>3.2514999999999992</v>
       </c>
-      <c r="T32" s="10">
+      <c r="T32" s="25">
         <f>+T30-T31</f>
         <v>12.372999999999999</v>
       </c>
-      <c r="U32" s="10">
+      <c r="U32" s="25">
         <f>+U30-U31</f>
         <v>18.613</v>
       </c>
-      <c r="V32" s="10">
-        <f>+V30*0.5</f>
-        <v>13.5</v>
+      <c r="V32" s="25">
+        <f>+V30-V31</f>
+        <v>18.296999999999997</v>
       </c>
       <c r="AD32" s="10">
         <f>+AD30-AD31</f>
@@ -4154,47 +4176,47 @@
       </c>
       <c r="AI32" s="10">
         <f>+AI30*0.7</f>
-        <v>57.287089999999999</v>
+        <v>91.015749999999983</v>
       </c>
       <c r="AJ32" s="10">
         <f t="shared" ref="AJ32:AS32" si="16">+AJ30*0.7</f>
-        <v>108.84547099999999</v>
+        <v>172.92992499999997</v>
       </c>
       <c r="AK32" s="10">
         <f t="shared" si="16"/>
-        <v>206.80639489999999</v>
+        <v>328.56685749999991</v>
       </c>
       <c r="AL32" s="10">
         <f t="shared" si="16"/>
-        <v>392.93215031</v>
+        <v>624.27702924999983</v>
       </c>
       <c r="AM32" s="10">
         <f t="shared" si="16"/>
-        <v>746.57108558899995</v>
+        <v>1186.1263555749995</v>
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="16"/>
-        <v>821.22819414790001</v>
+        <v>1304.7389911324995</v>
       </c>
       <c r="AO32" s="10">
         <f t="shared" si="16"/>
-        <v>903.35101356269001</v>
+        <v>1435.2128902457498</v>
       </c>
       <c r="AP32" s="10">
         <f t="shared" si="16"/>
-        <v>993.68611491895911</v>
+        <v>1578.7341792703251</v>
       </c>
       <c r="AQ32" s="10">
         <f t="shared" si="16"/>
-        <v>1093.0547264108552</v>
+        <v>1736.6075971973576</v>
       </c>
       <c r="AR32" s="10">
         <f t="shared" si="16"/>
-        <v>1202.360199051941</v>
+        <v>1910.2683569170933</v>
       </c>
       <c r="AS32" s="10">
         <f t="shared" si="16"/>
-        <v>1322.5962189571351</v>
+        <v>2101.2951926088031</v>
       </c>
     </row>
     <row r="33" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4253,8 +4275,7 @@
         <v>66.298000000000002</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33:V35" si="17">+R33</f>
-        <v>40.076999999999998</v>
+        <v>96.094999999999999</v>
       </c>
       <c r="AD33" s="10">
         <v>10.157</v>
@@ -4269,7 +4290,7 @@
         <v>92.320999999999998</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33:AH35" si="18">SUM(O33:R33)</f>
+        <f t="shared" ref="AH33:AH35" si="17">SUM(O33:R33)</f>
         <v>136.827</v>
       </c>
       <c r="AI33" s="10">
@@ -4277,43 +4298,43 @@
         <v>143.66835</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33:AS33" si="19">+AI33*1.05</f>
+        <f t="shared" ref="AJ33:AS33" si="18">+AI33*1.05</f>
         <v>150.85176750000002</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>158.39435587500003</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>166.31407366875004</v>
       </c>
       <c r="AM33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>174.62977735218755</v>
       </c>
       <c r="AN33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>183.36126621979693</v>
       </c>
       <c r="AO33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>192.52932953078678</v>
       </c>
       <c r="AP33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>202.15579600732613</v>
       </c>
       <c r="AQ33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>212.26358580769244</v>
       </c>
       <c r="AR33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>222.87676509807707</v>
       </c>
       <c r="AS33" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>234.02060335298094</v>
       </c>
     </row>
@@ -4373,8 +4394,7 @@
         <v>14.441000000000001</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="17"/>
-        <v>8.9269999999999996</v>
+        <v>19.518999999999998</v>
       </c>
       <c r="AD34" s="10">
         <v>0.48599999999999999</v>
@@ -4389,51 +4409,51 @@
         <v>18.27</v>
       </c>
       <c r="AH34" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>28.395</v>
       </c>
       <c r="AI34" s="10">
-        <f t="shared" ref="AI34:AS34" si="20">+AH34*1.05</f>
+        <f t="shared" ref="AI34:AS34" si="19">+AH34*1.05</f>
         <v>29.81475</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>31.305487500000002</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>32.870761875000007</v>
       </c>
       <c r="AL34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>34.514299968750009</v>
       </c>
       <c r="AM34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>36.240014967187513</v>
       </c>
       <c r="AN34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>38.052015715546887</v>
       </c>
       <c r="AO34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>39.954616501324232</v>
       </c>
       <c r="AP34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>41.952347326390445</v>
       </c>
       <c r="AQ34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>44.04996469270997</v>
       </c>
       <c r="AR34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>46.252462927345469</v>
       </c>
       <c r="AS34" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>48.565086073712742</v>
       </c>
     </row>
@@ -4493,8 +4513,7 @@
         <v>82.504999999999995</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="17"/>
-        <v>29.66</v>
+        <v>90.668999999999997</v>
       </c>
       <c r="AD35" s="10">
         <v>3.5470000000000002</v>
@@ -4509,51 +4528,51 @@
         <v>50.722000000000001</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>72.323999999999998</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" ref="AI35:AS35" si="21">+AH35*1.05</f>
+        <f t="shared" ref="AI35:AS35" si="20">+AH35*1.05</f>
         <v>75.940200000000004</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>79.737210000000005</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>83.72407050000001</v>
       </c>
       <c r="AL35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>87.910274025000021</v>
       </c>
       <c r="AM35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>92.305787726250031</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>96.921077112562543</v>
       </c>
       <c r="AO35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>101.76713096819067</v>
       </c>
       <c r="AP35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>106.85548751660021</v>
       </c>
       <c r="AQ35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>112.19826189243022</v>
       </c>
       <c r="AR35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>117.80817498705174</v>
       </c>
       <c r="AS35" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>123.69858373640433</v>
       </c>
     </row>
@@ -4566,39 +4585,39 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11">
-        <f t="shared" ref="G36:J36" si="22">SUM(G33:G35)</f>
+        <f t="shared" ref="G36:J36" si="21">SUM(G33:G35)</f>
         <v>18.402999999999999</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>19.343</v>
       </c>
       <c r="I36" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>25.409999999999997</v>
       </c>
       <c r="J36" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>25.173000000000002</v>
       </c>
       <c r="K36" s="11">
-        <f t="shared" ref="K36" si="23">SUM(K33:K35)</f>
+        <f t="shared" ref="K36" si="22">SUM(K33:K35)</f>
         <v>29.480999999999998</v>
       </c>
       <c r="L36" s="11">
-        <f t="shared" ref="L36" si="24">SUM(L33:L35)</f>
+        <f t="shared" ref="L36" si="23">SUM(L33:L35)</f>
         <v>34.373999999999995</v>
       </c>
       <c r="M36" s="11">
-        <f t="shared" ref="M36:O36" si="25">SUM(M33:M35)</f>
+        <f t="shared" ref="M36:O36" si="24">SUM(M33:M35)</f>
         <v>43.573</v>
       </c>
       <c r="N36" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>53.884999999999991</v>
       </c>
       <c r="O36" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>53.088999999999999</v>
       </c>
       <c r="P36" s="11">
@@ -4618,16 +4637,16 @@
         <v>72.369</v>
       </c>
       <c r="T36" s="11">
-        <f t="shared" ref="T36:V36" si="26">SUM(T33:T35)</f>
+        <f t="shared" ref="T36:V36" si="25">SUM(T33:T35)</f>
         <v>162.34299999999999</v>
       </c>
       <c r="U36" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>163.244</v>
       </c>
       <c r="V36" s="11">
-        <f t="shared" si="26"/>
-        <v>78.664000000000001</v>
+        <f t="shared" si="25"/>
+        <v>206.28300000000002</v>
       </c>
       <c r="W36" s="11"/>
       <c r="X36" s="11"/>
@@ -4637,67 +4656,67 @@
       <c r="AB36" s="11"/>
       <c r="AC36" s="11"/>
       <c r="AD36" s="11">
-        <f t="shared" ref="AD36:AE36" si="27">SUM(AD33:AD35)</f>
+        <f t="shared" ref="AD36:AE36" si="26">SUM(AD33:AD35)</f>
         <v>14.190000000000001</v>
       </c>
       <c r="AE36" s="11">
+        <f t="shared" si="26"/>
+        <v>37.198</v>
+      </c>
+      <c r="AF36" s="11">
+        <f t="shared" ref="AF36:AH36" si="27">SUM(AF33:AF35)</f>
+        <v>88.329000000000008</v>
+      </c>
+      <c r="AG36" s="11">
         <f t="shared" si="27"/>
-        <v>37.198</v>
-      </c>
-      <c r="AF36" s="11">
-        <f t="shared" ref="AF36:AH36" si="28">SUM(AF33:AF35)</f>
-        <v>88.329000000000008</v>
-      </c>
-      <c r="AG36" s="11">
-        <f t="shared" si="28"/>
         <v>161.31299999999999</v>
       </c>
       <c r="AH36" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>237.54599999999999</v>
       </c>
       <c r="AI36" s="11">
-        <f t="shared" ref="AI36" si="29">SUM(AI33:AI35)</f>
+        <f t="shared" ref="AI36" si="28">SUM(AI33:AI35)</f>
         <v>249.42330000000001</v>
       </c>
       <c r="AJ36" s="11">
-        <f t="shared" ref="AJ36" si="30">SUM(AJ33:AJ35)</f>
+        <f t="shared" ref="AJ36" si="29">SUM(AJ33:AJ35)</f>
         <v>261.89446500000003</v>
       </c>
       <c r="AK36" s="11">
-        <f t="shared" ref="AK36" si="31">SUM(AK33:AK35)</f>
+        <f t="shared" ref="AK36" si="30">SUM(AK33:AK35)</f>
         <v>274.98918825000004</v>
       </c>
       <c r="AL36" s="11">
-        <f t="shared" ref="AL36" si="32">SUM(AL33:AL35)</f>
+        <f t="shared" ref="AL36" si="31">SUM(AL33:AL35)</f>
         <v>288.73864766250006</v>
       </c>
       <c r="AM36" s="11">
-        <f t="shared" ref="AM36" si="33">SUM(AM33:AM35)</f>
+        <f t="shared" ref="AM36" si="32">SUM(AM33:AM35)</f>
         <v>303.17558004562511</v>
       </c>
       <c r="AN36" s="11">
-        <f t="shared" ref="AN36" si="34">SUM(AN33:AN35)</f>
+        <f t="shared" ref="AN36" si="33">SUM(AN33:AN35)</f>
         <v>318.33435904790639</v>
       </c>
       <c r="AO36" s="11">
-        <f t="shared" ref="AO36" si="35">SUM(AO33:AO35)</f>
+        <f t="shared" ref="AO36" si="34">SUM(AO33:AO35)</f>
         <v>334.25107700030168</v>
       </c>
       <c r="AP36" s="11">
-        <f t="shared" ref="AP36" si="36">SUM(AP33:AP35)</f>
+        <f t="shared" ref="AP36" si="35">SUM(AP33:AP35)</f>
         <v>350.9636308503168</v>
       </c>
       <c r="AQ36" s="11">
-        <f t="shared" ref="AQ36" si="37">SUM(AQ33:AQ35)</f>
+        <f t="shared" ref="AQ36" si="36">SUM(AQ33:AQ35)</f>
         <v>368.51181239283267</v>
       </c>
       <c r="AR36" s="11">
-        <f t="shared" ref="AR36" si="38">SUM(AR33:AR35)</f>
+        <f t="shared" ref="AR36" si="37">SUM(AR33:AR35)</f>
         <v>386.93740301247431</v>
       </c>
       <c r="AS36" s="11">
-        <f t="shared" ref="AS36" si="39">SUM(AS33:AS35)</f>
+        <f t="shared" ref="AS36" si="38">SUM(AS33:AS35)</f>
         <v>406.28427316309802</v>
       </c>
     </row>
@@ -4710,43 +4729,43 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11">
-        <f t="shared" ref="G37:J37" si="40">+G32-G36</f>
+        <f t="shared" ref="G37:J37" si="39">+G32-G36</f>
         <v>-17.017999999999997</v>
       </c>
       <c r="H37" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>-17.477</v>
       </c>
       <c r="I37" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>-23.379999999999995</v>
       </c>
       <c r="J37" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>-22.274000000000001</v>
       </c>
       <c r="K37" s="11">
-        <f t="shared" ref="K37" si="41">+K32-K36</f>
+        <f t="shared" ref="K37" si="40">+K32-K36</f>
         <v>-26.216999999999999</v>
       </c>
       <c r="L37" s="11">
-        <f t="shared" ref="L37" si="42">+L32-L36</f>
+        <f t="shared" ref="L37" si="41">+L32-L36</f>
         <v>-30.774999999999995</v>
       </c>
       <c r="M37" s="11">
-        <f t="shared" ref="M37:P37" si="43">+M32-M36</f>
+        <f t="shared" ref="M37:P37" si="42">+M32-M36</f>
         <v>-39.445</v>
       </c>
       <c r="N37" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>-50.941999999999986</v>
       </c>
       <c r="O37" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>-48.920999999999999</v>
       </c>
       <c r="P37" s="11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>-45.904999999999994</v>
       </c>
       <c r="Q37" s="11">
@@ -4762,16 +4781,16 @@
         <v>-69.117500000000007</v>
       </c>
       <c r="T37" s="11">
-        <f t="shared" ref="T37:V37" si="44">+T32-T36</f>
+        <f t="shared" ref="T37:V37" si="43">+T32-T36</f>
         <v>-149.97</v>
       </c>
       <c r="U37" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>-144.631</v>
       </c>
       <c r="V37" s="11">
-        <f t="shared" si="44"/>
-        <v>-65.164000000000001</v>
+        <f t="shared" si="43"/>
+        <v>-187.98600000000002</v>
       </c>
       <c r="W37" s="11"/>
       <c r="X37" s="11"/>
@@ -4781,68 +4800,68 @@
       <c r="AB37" s="11"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="11">
-        <f t="shared" ref="AD37:AE37" si="45">+AD32-AD36</f>
+        <f t="shared" ref="AD37:AE37" si="44">+AD32-AD36</f>
         <v>-14.333000000000002</v>
       </c>
       <c r="AE37" s="11">
+        <f t="shared" si="44"/>
+        <v>-36.139000000000003</v>
+      </c>
+      <c r="AF37" s="11">
+        <f t="shared" ref="AF37:AH37" si="45">+AF32-AF36</f>
+        <v>-80.14200000000001</v>
+      </c>
+      <c r="AG37" s="11">
         <f t="shared" si="45"/>
-        <v>-36.139000000000003</v>
-      </c>
-      <c r="AF37" s="11">
-        <f t="shared" ref="AF37:AH37" si="46">+AF32-AF36</f>
-        <v>-80.14200000000001</v>
-      </c>
-      <c r="AG37" s="11">
-        <f t="shared" si="46"/>
         <v>-147.37899999999999</v>
       </c>
       <c r="AH37" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-215.07</v>
       </c>
       <c r="AI37" s="11">
-        <f t="shared" ref="AI37" si="47">+AI32-AI36</f>
-        <v>-192.13621000000001</v>
+        <f t="shared" ref="AI37" si="46">+AI32-AI36</f>
+        <v>-158.40755000000001</v>
       </c>
       <c r="AJ37" s="11">
-        <f t="shared" ref="AJ37" si="48">+AJ32-AJ36</f>
-        <v>-153.04899400000005</v>
+        <f t="shared" ref="AJ37" si="47">+AJ32-AJ36</f>
+        <v>-88.964540000000056</v>
       </c>
       <c r="AK37" s="11">
-        <f t="shared" ref="AK37" si="49">+AK32-AK36</f>
-        <v>-68.182793350000054</v>
+        <f t="shared" ref="AK37" si="48">+AK32-AK36</f>
+        <v>53.577669249999872</v>
       </c>
       <c r="AL37" s="11">
-        <f t="shared" ref="AL37" si="50">+AL32-AL36</f>
-        <v>104.19350264749994</v>
+        <f t="shared" ref="AL37" si="49">+AL32-AL36</f>
+        <v>335.53838158749977</v>
       </c>
       <c r="AM37" s="11">
-        <f t="shared" ref="AM37" si="51">+AM32-AM36</f>
-        <v>443.39550554337484</v>
+        <f t="shared" ref="AM37" si="50">+AM32-AM36</f>
+        <v>882.95077552937437</v>
       </c>
       <c r="AN37" s="11">
-        <f t="shared" ref="AN37" si="52">+AN32-AN36</f>
-        <v>502.89383509999362</v>
+        <f t="shared" ref="AN37" si="51">+AN32-AN36</f>
+        <v>986.404632084593</v>
       </c>
       <c r="AO37" s="11">
-        <f t="shared" ref="AO37" si="53">+AO32-AO36</f>
-        <v>569.09993656238839</v>
+        <f t="shared" ref="AO37" si="52">+AO32-AO36</f>
+        <v>1100.9618132454482</v>
       </c>
       <c r="AP37" s="11">
-        <f t="shared" ref="AP37" si="54">+AP32-AP36</f>
-        <v>642.7224840686423</v>
+        <f t="shared" ref="AP37" si="53">+AP32-AP36</f>
+        <v>1227.7705484200083</v>
       </c>
       <c r="AQ37" s="11">
-        <f t="shared" ref="AQ37" si="55">+AQ32-AQ36</f>
-        <v>724.54291401802254</v>
+        <f t="shared" ref="AQ37" si="54">+AQ32-AQ36</f>
+        <v>1368.095784804525</v>
       </c>
       <c r="AR37" s="11">
-        <f t="shared" ref="AR37" si="56">+AR32-AR36</f>
-        <v>815.42279603946668</v>
+        <f t="shared" ref="AR37" si="55">+AR32-AR36</f>
+        <v>1523.330953904619</v>
       </c>
       <c r="AS37" s="11">
-        <f t="shared" ref="AS37" si="57">+AS32-AS36</f>
-        <v>916.311945794037</v>
+        <f t="shared" ref="AS37" si="56">+AS32-AS36</f>
+        <v>1695.010919445705</v>
       </c>
     </row>
     <row r="38" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4903,11 +4922,10 @@
         <v>14.436999999999999</v>
       </c>
       <c r="V38" s="10">
-        <f>+U38</f>
-        <v>14.436999999999999</v>
+        <v>29.257999999999999</v>
       </c>
       <c r="AH38" s="10">
-        <f t="shared" ref="AH38" si="58">SUM(O38:R38)</f>
+        <f t="shared" ref="AH38" si="57">SUM(O38:R38)</f>
         <v>18.153000000000002</v>
       </c>
     </row>
@@ -4916,27 +4934,27 @@
         <v>59</v>
       </c>
       <c r="G39" s="11">
-        <f t="shared" ref="G39:J39" si="59">+G37+G38</f>
+        <f t="shared" ref="G39:J39" si="58">+G37+G38</f>
         <v>-16.409999999999997</v>
       </c>
       <c r="H39" s="11">
+        <f t="shared" si="58"/>
+        <v>-16.218</v>
+      </c>
+      <c r="I39" s="11">
+        <f t="shared" si="58"/>
+        <v>-21.320999999999994</v>
+      </c>
+      <c r="J39" s="11">
+        <f t="shared" si="58"/>
+        <v>-19.106999999999999</v>
+      </c>
+      <c r="K39" s="11">
+        <f t="shared" ref="K39:L39" si="59">+K37+K38</f>
+        <v>-21.985999999999997</v>
+      </c>
+      <c r="L39" s="11">
         <f t="shared" si="59"/>
-        <v>-16.218</v>
-      </c>
-      <c r="I39" s="11">
-        <f t="shared" si="59"/>
-        <v>-21.320999999999994</v>
-      </c>
-      <c r="J39" s="11">
-        <f t="shared" si="59"/>
-        <v>-19.106999999999999</v>
-      </c>
-      <c r="K39" s="11">
-        <f t="shared" ref="K39:L39" si="60">+K37+K38</f>
-        <v>-21.985999999999997</v>
-      </c>
-      <c r="L39" s="11">
-        <f t="shared" si="60"/>
         <v>-25.897999999999996</v>
       </c>
       <c r="M39" s="11">
@@ -4944,40 +4962,40 @@
         <v>-34.438000000000002</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" ref="N39:P39" si="61">+N37+N38</f>
+        <f t="shared" ref="N39:P39" si="60">+N37+N38</f>
         <v>-45.969999999999985</v>
       </c>
       <c r="O39" s="11">
+        <f t="shared" si="60"/>
+        <v>-44.122</v>
+      </c>
+      <c r="P39" s="11">
+        <f t="shared" si="60"/>
+        <v>-41.103999999999992</v>
+      </c>
+      <c r="Q39" s="11">
+        <f t="shared" ref="Q39:V39" si="61">+Q37+Q38</f>
+        <v>-43.721999999999994</v>
+      </c>
+      <c r="R39" s="11">
         <f t="shared" si="61"/>
-        <v>-44.122</v>
-      </c>
-      <c r="P39" s="11">
+        <v>-67.968999999999994</v>
+      </c>
+      <c r="S39" s="11">
         <f t="shared" si="61"/>
-        <v>-41.103999999999992</v>
-      </c>
-      <c r="Q39" s="11">
-        <f t="shared" ref="Q39:V39" si="62">+Q37+Q38</f>
-        <v>-43.721999999999994</v>
-      </c>
-      <c r="R39" s="11">
-        <f t="shared" si="62"/>
-        <v>-67.968999999999994</v>
-      </c>
-      <c r="S39" s="11">
-        <f t="shared" si="62"/>
         <v>-64.223500000000001</v>
       </c>
       <c r="T39" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>-142.83199999999999</v>
       </c>
       <c r="U39" s="11">
-        <f t="shared" si="62"/>
+        <f t="shared" si="61"/>
         <v>-130.19399999999999</v>
       </c>
       <c r="V39" s="11">
-        <f t="shared" si="62"/>
-        <v>-50.727000000000004</v>
+        <f t="shared" si="61"/>
+        <v>-158.72800000000001</v>
       </c>
       <c r="W39" s="11"/>
       <c r="X39" s="11"/>
@@ -4987,68 +5005,68 @@
       <c r="AB39" s="11"/>
       <c r="AC39" s="11"/>
       <c r="AD39" s="11">
-        <f t="shared" ref="AD39:AH39" si="63">+AD37+AD38</f>
+        <f t="shared" ref="AD39:AH39" si="62">+AD37+AD38</f>
         <v>-14.333000000000002</v>
       </c>
       <c r="AE39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>-36.139000000000003</v>
       </c>
       <c r="AF39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>-80.14200000000001</v>
       </c>
       <c r="AG39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>-147.37899999999999</v>
       </c>
       <c r="AH39" s="11">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>-196.917</v>
       </c>
       <c r="AI39" s="11">
-        <f t="shared" ref="AI39" si="64">+AI37+AI38</f>
-        <v>-192.13621000000001</v>
+        <f t="shared" ref="AI39" si="63">+AI37+AI38</f>
+        <v>-158.40755000000001</v>
       </c>
       <c r="AJ39" s="11">
-        <f t="shared" ref="AJ39" si="65">+AJ37+AJ38</f>
-        <v>-153.04899400000005</v>
+        <f t="shared" ref="AJ39" si="64">+AJ37+AJ38</f>
+        <v>-88.964540000000056</v>
       </c>
       <c r="AK39" s="11">
-        <f t="shared" ref="AK39" si="66">+AK37+AK38</f>
-        <v>-68.182793350000054</v>
+        <f t="shared" ref="AK39" si="65">+AK37+AK38</f>
+        <v>53.577669249999872</v>
       </c>
       <c r="AL39" s="11">
-        <f t="shared" ref="AL39" si="67">+AL37+AL38</f>
-        <v>104.19350264749994</v>
+        <f t="shared" ref="AL39" si="66">+AL37+AL38</f>
+        <v>335.53838158749977</v>
       </c>
       <c r="AM39" s="11">
-        <f t="shared" ref="AM39" si="68">+AM37+AM38</f>
-        <v>443.39550554337484</v>
+        <f t="shared" ref="AM39" si="67">+AM37+AM38</f>
+        <v>882.95077552937437</v>
       </c>
       <c r="AN39" s="11">
-        <f t="shared" ref="AN39" si="69">+AN37+AN38</f>
-        <v>502.89383509999362</v>
+        <f t="shared" ref="AN39" si="68">+AN37+AN38</f>
+        <v>986.404632084593</v>
       </c>
       <c r="AO39" s="11">
-        <f t="shared" ref="AO39" si="70">+AO37+AO38</f>
-        <v>569.09993656238839</v>
+        <f t="shared" ref="AO39" si="69">+AO37+AO38</f>
+        <v>1100.9618132454482</v>
       </c>
       <c r="AP39" s="11">
-        <f t="shared" ref="AP39" si="71">+AP37+AP38</f>
-        <v>642.7224840686423</v>
+        <f t="shared" ref="AP39" si="70">+AP37+AP38</f>
+        <v>1227.7705484200083</v>
       </c>
       <c r="AQ39" s="11">
-        <f t="shared" ref="AQ39" si="72">+AQ37+AQ38</f>
-        <v>724.54291401802254</v>
+        <f t="shared" ref="AQ39" si="71">+AQ37+AQ38</f>
+        <v>1368.095784804525</v>
       </c>
       <c r="AR39" s="11">
-        <f t="shared" ref="AR39" si="73">+AR37+AR38</f>
-        <v>815.42279603946668</v>
+        <f t="shared" ref="AR39" si="72">+AR37+AR38</f>
+        <v>1523.330953904619</v>
       </c>
       <c r="AS39" s="11">
-        <f t="shared" ref="AS39" si="74">+AS37+AS38</f>
-        <v>916.311945794037</v>
+        <f t="shared" ref="AS39" si="73">+AS37+AS38</f>
+        <v>1695.010919445705</v>
       </c>
     </row>
     <row r="40" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -5108,40 +5126,40 @@
         <v>0</v>
       </c>
       <c r="AH40" s="10">
-        <f t="shared" ref="AH40" si="75">SUM(O40:R40)</f>
+        <f t="shared" ref="AH40" si="74">SUM(O40:R40)</f>
         <v>0</v>
       </c>
       <c r="AL40" s="10">
         <f>+AL39*0.1</f>
-        <v>10.419350264749994</v>
+        <v>33.553838158749976</v>
       </c>
       <c r="AM40" s="10">
-        <f t="shared" ref="AM40:AS40" si="76">+AM39*0.1</f>
-        <v>44.339550554337485</v>
+        <f t="shared" ref="AM40:AS40" si="75">+AM39*0.1</f>
+        <v>88.295077552937443</v>
       </c>
       <c r="AN40" s="10">
-        <f t="shared" si="76"/>
-        <v>50.289383509999368</v>
+        <f t="shared" si="75"/>
+        <v>98.640463208459309</v>
       </c>
       <c r="AO40" s="10">
-        <f t="shared" si="76"/>
-        <v>56.909993656238839</v>
+        <f t="shared" si="75"/>
+        <v>110.09618132454483</v>
       </c>
       <c r="AP40" s="10">
-        <f t="shared" si="76"/>
-        <v>64.272248406864236</v>
+        <f t="shared" si="75"/>
+        <v>122.77705484200084</v>
       </c>
       <c r="AQ40" s="10">
-        <f t="shared" si="76"/>
-        <v>72.454291401802251</v>
+        <f t="shared" si="75"/>
+        <v>136.8095784804525</v>
       </c>
       <c r="AR40" s="10">
-        <f t="shared" si="76"/>
-        <v>81.542279603946668</v>
+        <f t="shared" si="75"/>
+        <v>152.33309539046192</v>
       </c>
       <c r="AS40" s="10">
-        <f t="shared" si="76"/>
-        <v>91.631194579403711</v>
+        <f t="shared" si="75"/>
+        <v>169.5010919445705</v>
       </c>
     </row>
     <row r="41" spans="2:82" x14ac:dyDescent="0.25">
@@ -5149,19 +5167,19 @@
         <v>61</v>
       </c>
       <c r="G41" s="11">
-        <f t="shared" ref="G41:J41" si="77">+G39-G40</f>
+        <f t="shared" ref="G41:J41" si="76">+G39-G40</f>
         <v>-16.409999999999997</v>
       </c>
       <c r="H41" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>-16.218</v>
       </c>
       <c r="I41" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>-21.320999999999994</v>
       </c>
       <c r="J41" s="11">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>-19.106999999999999</v>
       </c>
       <c r="K41" s="11">
@@ -5169,48 +5187,48 @@
         <v>-21.985999999999997</v>
       </c>
       <c r="L41" s="11">
-        <f t="shared" ref="L41" si="78">+L39-L40</f>
+        <f t="shared" ref="L41" si="77">+L39-L40</f>
         <v>-25.897999999999996</v>
       </c>
       <c r="M41" s="11">
-        <f t="shared" ref="M41:V41" si="79">+M39-M40</f>
+        <f t="shared" ref="M41:V41" si="78">+M39-M40</f>
         <v>-34.438000000000002</v>
       </c>
       <c r="N41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-45.960999999999984</v>
       </c>
       <c r="O41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-44.122</v>
       </c>
       <c r="P41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-41.103999999999992</v>
       </c>
       <c r="Q41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-43.721999999999994</v>
       </c>
       <c r="R41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-67.968999999999994</v>
       </c>
       <c r="S41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-64.223500000000001</v>
       </c>
       <c r="T41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-142.83199999999999</v>
       </c>
       <c r="U41" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-130.19399999999999</v>
       </c>
       <c r="V41" s="11">
-        <f t="shared" si="79"/>
-        <v>-50.727000000000004</v>
+        <f t="shared" si="78"/>
+        <v>-158.72800000000001</v>
       </c>
       <c r="W41" s="11"/>
       <c r="X41" s="11"/>
@@ -5220,216 +5238,216 @@
       <c r="AB41" s="11"/>
       <c r="AC41" s="11"/>
       <c r="AD41" s="11">
-        <f t="shared" ref="AD41:AH41" si="80">+AD39-AD40</f>
+        <f t="shared" ref="AD41:AH41" si="79">+AD39-AD40</f>
         <v>-14.333000000000002</v>
       </c>
       <c r="AE41" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-36.139000000000003</v>
       </c>
       <c r="AF41" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-80.14200000000001</v>
       </c>
       <c r="AG41" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-147.37899999999999</v>
       </c>
       <c r="AH41" s="11">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>-196.917</v>
       </c>
       <c r="AI41" s="11">
-        <f t="shared" ref="AI41" si="81">+AI39-AI40</f>
-        <v>-192.13621000000001</v>
+        <f t="shared" ref="AI41" si="80">+AI39-AI40</f>
+        <v>-158.40755000000001</v>
       </c>
       <c r="AJ41" s="11">
-        <f t="shared" ref="AJ41" si="82">+AJ39-AJ40</f>
-        <v>-153.04899400000005</v>
+        <f t="shared" ref="AJ41" si="81">+AJ39-AJ40</f>
+        <v>-88.964540000000056</v>
       </c>
       <c r="AK41" s="11">
-        <f t="shared" ref="AK41" si="83">+AK39-AK40</f>
-        <v>-68.182793350000054</v>
+        <f t="shared" ref="AK41" si="82">+AK39-AK40</f>
+        <v>53.577669249999872</v>
       </c>
       <c r="AL41" s="11">
-        <f t="shared" ref="AL41" si="84">+AL39-AL40</f>
-        <v>93.774152382749946</v>
+        <f t="shared" ref="AL41" si="83">+AL39-AL40</f>
+        <v>301.98454342874982</v>
       </c>
       <c r="AM41" s="11">
-        <f t="shared" ref="AM41" si="85">+AM39-AM40</f>
-        <v>399.05595498903733</v>
+        <f t="shared" ref="AM41" si="84">+AM39-AM40</f>
+        <v>794.65569797643695</v>
       </c>
       <c r="AN41" s="11">
-        <f t="shared" ref="AN41" si="86">+AN39-AN40</f>
-        <v>452.60445158999426</v>
+        <f t="shared" ref="AN41" si="85">+AN39-AN40</f>
+        <v>887.76416887613368</v>
       </c>
       <c r="AO41" s="11">
-        <f t="shared" ref="AO41" si="87">+AO39-AO40</f>
-        <v>512.18994290614955</v>
+        <f t="shared" ref="AO41" si="86">+AO39-AO40</f>
+        <v>990.8656319209033</v>
       </c>
       <c r="AP41" s="11">
-        <f t="shared" ref="AP41" si="88">+AP39-AP40</f>
-        <v>578.45023566177804</v>
+        <f t="shared" ref="AP41" si="87">+AP39-AP40</f>
+        <v>1104.9934935780075</v>
       </c>
       <c r="AQ41" s="11">
-        <f t="shared" ref="AQ41" si="89">+AQ39-AQ40</f>
-        <v>652.08862261622028</v>
+        <f t="shared" ref="AQ41" si="88">+AQ39-AQ40</f>
+        <v>1231.2862063240725</v>
       </c>
       <c r="AR41" s="11">
-        <f t="shared" ref="AR41" si="90">+AR39-AR40</f>
-        <v>733.88051643552001</v>
+        <f t="shared" ref="AR41" si="89">+AR39-AR40</f>
+        <v>1370.9978585141571</v>
       </c>
       <c r="AS41" s="11">
-        <f t="shared" ref="AS41" si="91">+AS39-AS40</f>
-        <v>824.68075121463335</v>
+        <f t="shared" ref="AS41" si="90">+AS39-AS40</f>
+        <v>1525.5098275011344</v>
       </c>
       <c r="AT41" s="11">
         <f>+AS41*(1+$AT$48)</f>
-        <v>816.433943702487</v>
+        <v>1510.2547292261231</v>
       </c>
       <c r="AU41" s="11">
-        <f t="shared" ref="AU41:CD41" si="92">+AT41*(1+$AT$48)</f>
-        <v>808.26960426546214</v>
+        <f t="shared" ref="AU41:CD41" si="91">+AT41*(1+$AT$48)</f>
+        <v>1495.1521819338618</v>
       </c>
       <c r="AV41" s="11">
-        <f t="shared" si="92"/>
-        <v>800.18690822280746</v>
+        <f t="shared" si="91"/>
+        <v>1480.2006601145231</v>
       </c>
       <c r="AW41" s="11">
-        <f t="shared" si="92"/>
-        <v>792.18503914057942</v>
+        <f t="shared" si="91"/>
+        <v>1465.3986535133779</v>
       </c>
       <c r="AX41" s="11">
-        <f t="shared" si="92"/>
-        <v>784.26318874917365</v>
+        <f t="shared" si="91"/>
+        <v>1450.7446669782441</v>
       </c>
       <c r="AY41" s="11">
-        <f t="shared" si="92"/>
-        <v>776.42055686168192</v>
+        <f t="shared" si="91"/>
+        <v>1436.2372203084617</v>
       </c>
       <c r="AZ41" s="11">
-        <f t="shared" si="92"/>
-        <v>768.65635129306509</v>
+        <f t="shared" si="91"/>
+        <v>1421.8748481053772</v>
       </c>
       <c r="BA41" s="11">
-        <f t="shared" si="92"/>
-        <v>760.96978778013442</v>
+        <f t="shared" si="91"/>
+        <v>1407.6560996243234</v>
       </c>
       <c r="BB41" s="11">
-        <f t="shared" si="92"/>
-        <v>753.36008990233313</v>
+        <f t="shared" si="91"/>
+        <v>1393.5795386280802</v>
       </c>
       <c r="BC41" s="11">
-        <f t="shared" si="92"/>
-        <v>745.8264890033098</v>
+        <f t="shared" si="91"/>
+        <v>1379.6437432417993</v>
       </c>
       <c r="BD41" s="11">
-        <f t="shared" si="92"/>
-        <v>738.36822411327671</v>
+        <f t="shared" si="91"/>
+        <v>1365.8473058093812</v>
       </c>
       <c r="BE41" s="11">
-        <f t="shared" si="92"/>
-        <v>730.98454187214395</v>
+        <f t="shared" si="91"/>
+        <v>1352.1888327512872</v>
       </c>
       <c r="BF41" s="11">
-        <f t="shared" si="92"/>
-        <v>723.67469645342248</v>
+        <f t="shared" si="91"/>
+        <v>1338.6669444237743</v>
       </c>
       <c r="BG41" s="11">
-        <f t="shared" si="92"/>
-        <v>716.43794948888831</v>
+        <f t="shared" si="91"/>
+        <v>1325.2802749795367</v>
       </c>
       <c r="BH41" s="11">
-        <f t="shared" si="92"/>
-        <v>709.27356999399944</v>
+        <f t="shared" si="91"/>
+        <v>1312.0274722297413</v>
       </c>
       <c r="BI41" s="11">
-        <f t="shared" si="92"/>
-        <v>702.18083429405942</v>
+        <f t="shared" si="91"/>
+        <v>1298.9071975074439</v>
       </c>
       <c r="BJ41" s="11">
-        <f t="shared" si="92"/>
-        <v>695.15902595111879</v>
+        <f t="shared" si="91"/>
+        <v>1285.9181255323695</v>
       </c>
       <c r="BK41" s="11">
-        <f t="shared" si="92"/>
-        <v>688.20743569160754</v>
+        <f t="shared" si="91"/>
+        <v>1273.0589442770458</v>
       </c>
       <c r="BL41" s="11">
-        <f t="shared" si="92"/>
-        <v>681.32536133469148</v>
+        <f t="shared" si="91"/>
+        <v>1260.3283548342754</v>
       </c>
       <c r="BM41" s="11">
-        <f t="shared" si="92"/>
-        <v>674.51210772134459</v>
+        <f t="shared" si="91"/>
+        <v>1247.7250712859327</v>
       </c>
       <c r="BN41" s="11">
-        <f t="shared" si="92"/>
-        <v>667.76698664413118</v>
+        <f t="shared" si="91"/>
+        <v>1235.2478205730733</v>
       </c>
       <c r="BO41" s="11">
-        <f t="shared" si="92"/>
-        <v>661.08931677768987</v>
+        <f t="shared" si="91"/>
+        <v>1222.8953423673427</v>
       </c>
       <c r="BP41" s="11">
-        <f t="shared" si="92"/>
-        <v>654.47842360991297</v>
+        <f t="shared" si="91"/>
+        <v>1210.6663889436693</v>
       </c>
       <c r="BQ41" s="11">
-        <f t="shared" si="92"/>
-        <v>647.93363937381378</v>
+        <f t="shared" si="91"/>
+        <v>1198.5597250542326</v>
       </c>
       <c r="BR41" s="11">
-        <f t="shared" si="92"/>
-        <v>641.45430298007568</v>
+        <f t="shared" si="91"/>
+        <v>1186.5741278036903</v>
       </c>
       <c r="BS41" s="11">
-        <f t="shared" si="92"/>
-        <v>635.03975995027497</v>
+        <f t="shared" si="91"/>
+        <v>1174.7083865256534</v>
       </c>
       <c r="BT41" s="11">
-        <f t="shared" si="92"/>
-        <v>628.68936235077217</v>
+        <f t="shared" si="91"/>
+        <v>1162.9613026603968</v>
       </c>
       <c r="BU41" s="11">
-        <f t="shared" si="92"/>
-        <v>622.40246872726448</v>
+        <f t="shared" si="91"/>
+        <v>1151.3316896337928</v>
       </c>
       <c r="BV41" s="11">
-        <f t="shared" si="92"/>
-        <v>616.17844403999186</v>
+        <f t="shared" si="91"/>
+        <v>1139.8183727374549</v>
       </c>
       <c r="BW41" s="11">
-        <f t="shared" si="92"/>
-        <v>610.01665959959189</v>
+        <f t="shared" si="91"/>
+        <v>1128.4201890100803</v>
       </c>
       <c r="BX41" s="11">
-        <f t="shared" si="92"/>
-        <v>603.91649300359597</v>
+        <f t="shared" si="91"/>
+        <v>1117.1359871199795</v>
       </c>
       <c r="BY41" s="11">
-        <f t="shared" si="92"/>
-        <v>597.87732807355997</v>
+        <f t="shared" si="91"/>
+        <v>1105.9646272487796</v>
       </c>
       <c r="BZ41" s="11">
-        <f t="shared" si="92"/>
-        <v>591.89855479282437</v>
+        <f t="shared" si="91"/>
+        <v>1094.9049809762919</v>
       </c>
       <c r="CA41" s="11">
-        <f t="shared" si="92"/>
-        <v>585.97956924489608</v>
+        <f t="shared" si="91"/>
+        <v>1083.9559311665289</v>
       </c>
       <c r="CB41" s="11">
-        <f t="shared" si="92"/>
-        <v>580.1197735524471</v>
+        <f t="shared" si="91"/>
+        <v>1073.1163718548637</v>
       </c>
       <c r="CC41" s="11">
-        <f t="shared" si="92"/>
-        <v>574.31857581692259</v>
+        <f t="shared" si="91"/>
+        <v>1062.385208136315</v>
       </c>
       <c r="CD41" s="11">
-        <f t="shared" si="92"/>
-        <v>568.57539005875333</v>
+        <f t="shared" si="91"/>
+        <v>1051.7613560549519</v>
       </c>
     </row>
     <row r="42" spans="2:82" x14ac:dyDescent="0.25">
@@ -5438,68 +5456,68 @@
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="12">
-        <f t="shared" ref="G42:J42" si="93">+G41/G43</f>
+        <f t="shared" ref="G42:J42" si="92">+G41/G43</f>
         <v>-8.3646286066414208E-2</v>
       </c>
       <c r="H42" s="12">
+        <f t="shared" si="92"/>
+        <v>-8.2235531913648616E-2</v>
+      </c>
+      <c r="I42" s="12">
+        <f t="shared" si="92"/>
+        <v>-0.10751836854075368</v>
+      </c>
+      <c r="J42" s="12">
+        <f t="shared" si="92"/>
+        <v>-9.4799827338986162E-2</v>
+      </c>
+      <c r="K42" s="12">
+        <f t="shared" ref="K42:V42" si="93">+K41/K43</f>
+        <v>-0.10986800423191202</v>
+      </c>
+      <c r="L42" s="12">
         <f t="shared" si="93"/>
-        <v>-8.2235531913648616E-2</v>
-      </c>
-      <c r="I42" s="12">
+        <v>-0.12856976575867524</v>
+      </c>
+      <c r="M42" s="12">
         <f t="shared" si="93"/>
-        <v>-0.10751836854075368</v>
-      </c>
-      <c r="J42" s="12">
+        <v>-0.16931970672379332</v>
+      </c>
+      <c r="N42" s="12">
         <f t="shared" si="93"/>
-        <v>-9.4799827338986162E-2</v>
-      </c>
-      <c r="K42" s="12">
-        <f t="shared" ref="K42:V42" si="94">+K41/K43</f>
-        <v>-0.10986800423191202</v>
-      </c>
-      <c r="L42" s="12">
-        <f t="shared" si="94"/>
-        <v>-0.12856976575867524</v>
-      </c>
-      <c r="M42" s="12">
-        <f t="shared" si="94"/>
-        <v>-0.16931970672379332</v>
-      </c>
-      <c r="N42" s="12">
-        <f t="shared" si="94"/>
         <v>-0.223866675624386</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.21196252359231235</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.19421890770112599</v>
       </c>
       <c r="Q42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.2040175879567338</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.31185961190539768</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.28074742414506099</v>
       </c>
       <c r="T42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.56912558642314792</v>
       </c>
       <c r="U42" s="12">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-0.44204768558935476</v>
       </c>
       <c r="V42" s="12">
-        <f t="shared" si="94"/>
-        <v>-0.1722333820828241</v>
+        <f t="shared" si="93"/>
+        <v>-0.43017709678955141</v>
       </c>
       <c r="W42" s="12"/>
       <c r="X42" s="12"/>
@@ -5507,16 +5525,16 @@
       <c r="Z42" s="12"/>
       <c r="AA42" s="12"/>
       <c r="AD42" s="1">
-        <f t="shared" ref="AD42:AG42" si="95">AD41/AD43</f>
+        <f t="shared" ref="AD42:AG42" si="94">AD41/AD43</f>
         <v>-0.12458592650845435</v>
       </c>
       <c r="AE42" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>-0.26261972091776725</v>
       </c>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>-0.72758198245627148</v>
       </c>
       <c r="AH42" s="1">
@@ -5525,47 +5543,47 @@
       </c>
       <c r="AI42" s="1">
         <f>AI41/AI43</f>
-        <v>-0.90199563758156653</v>
+        <v>-0.74365430160188906</v>
       </c>
       <c r="AJ42" s="1">
-        <f t="shared" ref="AJ42:AS42" si="96">AJ41/AJ43</f>
-        <v>-0.71849822021703968</v>
+        <f t="shared" ref="AJ42:AS42" si="95">AJ41/AJ43</f>
+        <v>-0.41764968185565243</v>
       </c>
       <c r="AK42" s="1">
-        <f t="shared" si="96"/>
-        <v>-0.3200884526650416</v>
+        <f t="shared" si="95"/>
+        <v>0.25152377022159395</v>
       </c>
       <c r="AL42" s="1">
-        <f t="shared" si="96"/>
-        <v>0.44022871257400942</v>
+        <f t="shared" si="95"/>
+        <v>1.4176856137101561</v>
       </c>
       <c r="AM42" s="1">
-        <f t="shared" si="96"/>
-        <v>1.8733935188534094</v>
+        <f t="shared" si="95"/>
+        <v>3.7305616310120877</v>
       </c>
       <c r="AN42" s="1">
-        <f t="shared" si="96"/>
-        <v>2.1247803362217468</v>
+        <f t="shared" si="95"/>
+        <v>4.1676652595962915</v>
       </c>
       <c r="AO42" s="1">
-        <f t="shared" si="96"/>
-        <v>2.4045082086010674</v>
+        <f t="shared" si="95"/>
+        <v>4.6516816243130688</v>
       </c>
       <c r="AP42" s="1">
-        <f t="shared" si="96"/>
-        <v>2.7155713601561771</v>
+        <f t="shared" si="95"/>
+        <v>5.18746211743938</v>
       </c>
       <c r="AQ42" s="1">
-        <f t="shared" si="96"/>
-        <v>3.0612714434015489</v>
+        <f t="shared" si="95"/>
+        <v>5.7803512764130716</v>
       </c>
       <c r="AR42" s="1">
-        <f t="shared" si="96"/>
-        <v>3.4452486823329456</v>
+        <f t="shared" si="95"/>
+        <v>6.4362364986456191</v>
       </c>
       <c r="AS42" s="1">
-        <f t="shared" si="96"/>
-        <v>3.8715161498870434</v>
+        <f t="shared" si="95"/>
+        <v>7.1616027478309849</v>
       </c>
     </row>
     <row r="43" spans="2:82" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -5622,8 +5640,7 @@
         <v>294.52478600000001</v>
       </c>
       <c r="V43" s="10">
-        <f>+U43</f>
-        <v>294.52478600000001</v>
+        <v>368.98291699999999</v>
       </c>
       <c r="AD43" s="10">
         <v>115.045097</v>
@@ -5644,43 +5661,43 @@
         <v>213.01234950000003</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" ref="AJ43:AS43" si="97">+AI43</f>
+        <f t="shared" ref="AJ43:AS43" si="96">+AI43</f>
         <v>213.01234950000003</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AM43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AN43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AO43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AP43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AQ43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AR43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
       <c r="AS43" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>213.01234950000003</v>
       </c>
     </row>
@@ -5696,52 +5713,52 @@
         <v>95</v>
       </c>
       <c r="K45" s="17">
-        <f t="shared" ref="K45" si="98">+K30/G30-1</f>
+        <f t="shared" ref="K45" si="97">+K30/G30-1</f>
         <v>1.2017409114183306</v>
       </c>
       <c r="L45" s="17">
-        <f t="shared" ref="L45" si="99">+L30/H30-1</f>
+        <f t="shared" ref="L45" si="98">+L30/H30-1</f>
         <v>1.1088957055214723</v>
       </c>
       <c r="M45" s="17">
-        <f t="shared" ref="M45" si="100">+M30/I30-1</f>
+        <f t="shared" ref="M45" si="99">+M30/I30-1</f>
         <v>1.2207745204487876</v>
       </c>
       <c r="N45" s="17">
-        <f t="shared" ref="N45:V45" si="101">+N30/J30-1</f>
+        <f t="shared" ref="N45:V45" si="100">+N30/J30-1</f>
         <v>0.60684210526315874</v>
       </c>
       <c r="O45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>0.7632558139534884</v>
       </c>
       <c r="P45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>1.0692727272727272</v>
       </c>
       <c r="Q45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>1.0208604954367666</v>
       </c>
       <c r="R45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>0.91778578447428694</v>
       </c>
       <c r="S45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>-2.0443154840411593E-3</v>
       </c>
       <c r="T45" s="17">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>0.8188208417538001</v>
       </c>
       <c r="U45" s="16">
-        <f t="shared" si="101"/>
+        <f t="shared" si="100"/>
         <v>2.2149999999999999</v>
       </c>
       <c r="V45" s="16">
-        <f t="shared" si="101"/>
-        <v>1.3057216054654139</v>
+        <f t="shared" si="100"/>
+        <v>4.2852263023057215</v>
       </c>
       <c r="W45" s="16"/>
       <c r="X45" s="16"/>
@@ -5756,52 +5773,52 @@
         <v>11</v>
       </c>
       <c r="K46" s="16">
-        <f t="shared" ref="K46:N46" si="102">+K32/K30</f>
+        <f t="shared" ref="K46:N46" si="101">+K32/K30</f>
         <v>0.7590697674418605</v>
       </c>
       <c r="L46" s="16">
+        <f t="shared" si="101"/>
+        <v>0.65436363636363637</v>
+      </c>
+      <c r="M46" s="16">
+        <f t="shared" si="101"/>
+        <v>0.67275097783572357</v>
+      </c>
+      <c r="N46" s="16">
+        <f t="shared" si="101"/>
+        <v>0.48198493285293165</v>
+      </c>
+      <c r="O46" s="16">
+        <f t="shared" ref="O46:V46" si="102">+O32/O30</f>
+        <v>0.54972302822474273</v>
+      </c>
+      <c r="P46" s="16">
         <f t="shared" si="102"/>
-        <v>0.65436363636363637</v>
-      </c>
-      <c r="M46" s="16">
+        <v>0.50593093752745799</v>
+      </c>
+      <c r="Q46" s="16">
         <f t="shared" si="102"/>
-        <v>0.67275097783572357</v>
-      </c>
-      <c r="N46" s="16">
+        <v>0.47459677419354845</v>
+      </c>
+      <c r="R46" s="16">
         <f t="shared" si="102"/>
-        <v>0.48198493285293165</v>
-      </c>
-      <c r="O46" s="16">
-        <f t="shared" ref="O46:V46" si="103">+O32/O30</f>
-        <v>0.54972302822474273</v>
-      </c>
-      <c r="P46" s="16">
-        <f t="shared" si="103"/>
-        <v>0.50593093752745799</v>
-      </c>
-      <c r="Q46" s="16">
-        <f t="shared" si="103"/>
-        <v>0.47459677419354845</v>
-      </c>
-      <c r="R46" s="16">
-        <f t="shared" si="103"/>
         <v>0.56917164816396248</v>
       </c>
       <c r="S46" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.42972312165466192</v>
       </c>
       <c r="T46" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.59772946859903375</v>
       </c>
       <c r="U46" s="16">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.46688907841268246</v>
       </c>
       <c r="V46" s="16">
-        <f t="shared" si="103"/>
-        <v>0.5</v>
+        <f t="shared" si="102"/>
+        <v>0.29563742123121661</v>
       </c>
       <c r="AF46" s="4"/>
       <c r="AG46" s="4"/>
@@ -5849,7 +5866,7 @@
       </c>
       <c r="AT49" s="4">
         <f>NPV(AT46,AI41:CD41)</f>
-        <v>2138.2325016748337</v>
+        <v>4553.2127023355706</v>
       </c>
     </row>
     <row r="50" spans="2:46" x14ac:dyDescent="0.25">
@@ -5858,7 +5875,7 @@
       </c>
       <c r="AT50" s="1">
         <f>AT49/Main!J3</f>
-        <v>6.0354379873799555</v>
+        <v>12.33990109719787</v>
       </c>
     </row>
     <row r="51" spans="2:46" s="7" customFormat="1" x14ac:dyDescent="0.25">
